--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -853,7 +853,7 @@
     <t>Encounter.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/KHOrganization)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/KAOrganization)
 </t>
   </si>
   <si>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1194,7 +1194,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedPatient)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedBasisPatientKlarname|https://elga.moped.at/StructureDefinition/MopedBasisPatientvbPK)
 </t>
   </si>
   <si>
@@ -2433,7 +2433,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="108.19921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="118.0859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedEncounterA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1892,7 +1892,7 @@
     <t>LKF: Transportart</t>
   </si>
   <si>
-    <t>Identifies whether a patient arrives at the reporting facility via ambulance and the type of ambulance that was used.</t>
+    <t>Identifies how the patient arrives at the reporting facility, for example via an ambulance or other mode of transport.</t>
   </si>
   <si>
     <t>Encounter.admission.extension:Transportart.id</t>
